--- a/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
+++ b/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="300" windowWidth="14880" windowHeight="7815"/>
@@ -11,13 +11,103 @@
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="125725"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+  <si>
+    <t>Icono</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Utilidad</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>CSS</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>Lenguages</t>
+  </si>
+  <si>
+    <t>Frameworks</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>NestJS</t>
+  </si>
+  <si>
+    <t>Librerias</t>
+  </si>
+  <si>
+    <t>primeng</t>
+  </si>
+  <si>
+    <t>tailwindcss</t>
+  </si>
+  <si>
+    <t>socket.io-client</t>
+  </si>
+  <si>
+    <t>material-symbols</t>
+  </si>
+  <si>
+    <t>primeicons</t>
+  </si>
+  <si>
+    <t>rxjs</t>
+  </si>
+  <si>
+    <t>argon2</t>
+  </si>
+  <si>
+    <t>nodemailer</t>
+  </si>
+  <si>
+    <t>pg</t>
+  </si>
+  <si>
+    <t>typeorm</t>
+  </si>
+  <si>
+    <t>websockets</t>
+  </si>
+  <si>
+    <t>Herramientas</t>
+  </si>
+  <si>
+    <t>Visual Studio Code</t>
+  </si>
+  <si>
+    <t>DiaDIagram</t>
+  </si>
+  <si>
+    <t>Figma</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -25,16 +115,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -42,12 +151,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -60,7 +218,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Oficina">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -98,7 +256,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Oficina">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -168,7 +326,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Oficina">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -342,9 +500,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="B2:U14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="10"/>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="10"/>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B6" s="3"/>
+      <c r="C6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="10"/>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="M7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
+      <c r="M11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21">
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>

--- a/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
+++ b/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="300" windowWidth="14880" windowHeight="7815"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>Icono</t>
   </si>
@@ -97,17 +97,176 @@
   </si>
   <si>
     <t>Figma</t>
+  </si>
+  <si>
+    <t>paint.NET</t>
+  </si>
+  <si>
+    <t>Microsfot excel</t>
+  </si>
+  <si>
+    <t>Microsoft word</t>
+  </si>
+  <si>
+    <t>Google drive</t>
+  </si>
+  <si>
+    <t>Resend</t>
+  </si>
+  <si>
+    <t>Lenguaje de marcado para estructurar el contenido de páginas web.</t>
+  </si>
+  <si>
+    <t>Crear la estructura base de interfaces web y aplicaciones.</t>
+  </si>
+  <si>
+    <t>Lenguaje de estilos para definir el diseño y apariencia visual.</t>
+  </si>
+  <si>
+    <t>Diseñar layouts, colores, tipografías y adaptabilidad responsive.</t>
+  </si>
+  <si>
+    <t>Superset de JavaScript que añade tipado estático y mejoras.</t>
+  </si>
+  <si>
+    <t>Desarrollo más seguro y mantenible en aplicaciones grandes.</t>
+  </si>
+  <si>
+    <t>Framework frontend basado en TypeScript para SPA.</t>
+  </si>
+  <si>
+    <t>Crear aplicaciones web escalables y estructuradas.</t>
+  </si>
+  <si>
+    <t>Framework backend para Node.js basado en arquitectura modular.</t>
+  </si>
+  <si>
+    <t>Construcción de APIs robustas y mantenibles.</t>
+  </si>
+  <si>
+    <t>Biblioteca de componentes UI para Angular.</t>
+  </si>
+  <si>
+    <t>Crear interfaces modernas y consistentes rápidamente.</t>
+  </si>
+  <si>
+    <t>Framework CSS basado en clases utilitarias.</t>
+  </si>
+  <si>
+    <t>Maquetación rápida y diseño flexible sin CSS tradicional.</t>
+  </si>
+  <si>
+    <t>Cliente para comunicación en tiempo real vía WebSockets.</t>
+  </si>
+  <si>
+    <t>Chats, notificaciones y eventos en tiempo real.</t>
+  </si>
+  <si>
+    <t>Iconos oficiales de Google Material Design.</t>
+  </si>
+  <si>
+    <t>Uso de iconografía consistente y moderna.</t>
+  </si>
+  <si>
+    <t>Conjunto de iconos para PrimeNG.</t>
+  </si>
+  <si>
+    <t>Iconografía integrada con componentes PrimeNG.</t>
+  </si>
+  <si>
+    <t>Librería de programación reactiva basada en observables.</t>
+  </si>
+  <si>
+    <t>Manejo de flujos de datos asíncronos en Angular.</t>
+  </si>
+  <si>
+    <t>Algoritmo de hashing seguro para contraseñas.</t>
+  </si>
+  <si>
+    <t>Protección de credenciales de usuarios.</t>
+  </si>
+  <si>
+    <t>Librería para envío de correos electrónicos en Node.js.</t>
+  </si>
+  <si>
+    <t>Envío de emails transaccionales.</t>
+  </si>
+  <si>
+    <t>Servicio y SDK para envío de emails modernos.</t>
+  </si>
+  <si>
+    <t>Envío fiable de correos con APIs simples.</t>
+  </si>
+  <si>
+    <t>Cliente PostgreSQL para Node.js.</t>
+  </si>
+  <si>
+    <t>Conexión y consultas a bases de datos PostgreSQL.</t>
+  </si>
+  <si>
+    <t>ORM para TypeScript y JavaScript.</t>
+  </si>
+  <si>
+    <t>Mapeo y gestión de bases de datos relacionales.</t>
+  </si>
+  <si>
+    <t>Protocolo de comunicación bidireccional en tiempo real.</t>
+  </si>
+  <si>
+    <t>Comunicación instantánea entre cliente y servidor.</t>
+  </si>
+  <si>
+    <t>Editor de código ligero y extensible.</t>
+  </si>
+  <si>
+    <t>Desarrollo y depuración de aplicaciones.</t>
+  </si>
+  <si>
+    <t>Herramienta para diagramas y esquemas.</t>
+  </si>
+  <si>
+    <t>Diseño de diagramas UML y flujos.</t>
+  </si>
+  <si>
+    <t>Plataforma de diseño colaborativo UI/UX.</t>
+  </si>
+  <si>
+    <t>Prototipado y diseño de interfaces.</t>
+  </si>
+  <si>
+    <t>Editor gráfico sencillo para imágenes.</t>
+  </si>
+  <si>
+    <t>Edición básica de imágenes y recursos.</t>
+  </si>
+  <si>
+    <t>Hoja de cálculo para análisis de datos.</t>
+  </si>
+  <si>
+    <t>Organización y análisis de información.</t>
+  </si>
+  <si>
+    <t>Procesador de textos.</t>
+  </si>
+  <si>
+    <t>Documentación y redacción técnica.</t>
+  </si>
+  <si>
+    <t>Servicio de almacenamiento en la nube.</t>
+  </si>
+  <si>
+    <t>Compartición y respaldo de archivos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -188,30 +347,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top style="medium">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="4"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -258,7 +499,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -290,9 +531,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -324,6 +566,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -499,172 +742,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:U14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:U14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="10" max="10" width="28.42578125" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="15" width="28.42578125" customWidth="1"/>
+    <col min="19" max="19" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27" customWidth="1"/>
+    <col min="21" max="21" width="28.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B2" t="s">
+    <row r="1" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10"/>
+      <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L2" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="L2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="R2" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="10"/>
+      <c r="R2" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B3" s="1" t="s">
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="10"/>
+    </row>
+    <row r="3" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+    <row r="4" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="10"/>
-      <c r="H4" t="s">
+      <c r="D4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" t="s">
+      <c r="I4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S4" t="s">
+      <c r="N4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B5" s="6"/>
-      <c r="C5" s="7" t="s">
+      <c r="T4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="10"/>
-      <c r="H5" t="s">
+      <c r="D5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M5" t="s">
+      <c r="I5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S5" t="s">
+      <c r="N5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="3"/>
+      <c r="S5" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B6" s="3"/>
-      <c r="C6" s="7" t="s">
+      <c r="T5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="10"/>
-      <c r="M6" t="s">
+      <c r="D6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S6" t="s">
+      <c r="N6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="2:21">
-      <c r="M7" t="s">
+      <c r="T6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="3"/>
+      <c r="M7" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="2:21">
-      <c r="M8" t="s">
+      <c r="N7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="1"/>
+      <c r="M8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="2:21">
-      <c r="M9" t="s">
+      <c r="N8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="3"/>
+      <c r="M9" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="2:21">
-      <c r="M10" t="s">
+      <c r="N9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="R9" s="3"/>
+      <c r="S9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="U9" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="1"/>
+      <c r="M10" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="2:21">
-      <c r="M11" t="s">
+      <c r="N10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="U10" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="3"/>
+      <c r="M11" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="2:21">
-      <c r="M12" t="s">
+      <c r="N11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="R11" s="3"/>
+      <c r="S11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="U11" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="1"/>
+      <c r="M12" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="2:21">
-      <c r="M13" t="s">
+      <c r="N12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="3"/>
+      <c r="M13" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="2:21">
-      <c r="M14" t="s">
+      <c r="N13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="1"/>
+      <c r="M14" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="N14" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="R2:U2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -672,9 +1119,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>

--- a/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
+++ b/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="300" windowWidth="14880" windowHeight="7815"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>Icono</t>
   </si>
@@ -256,17 +256,59 @@
   </si>
   <si>
     <t>Compartición y respaldo de archivos.</t>
+  </si>
+  <si>
+    <t>pgAdmin</t>
+  </si>
+  <si>
+    <t>Herramienta de administración y desarrollo para PostgreSQL.</t>
+  </si>
+  <si>
+    <t>Gestión de bases de datos, ejecución de consultas SQL y diseño de esquemas.</t>
+  </si>
+  <si>
+    <t>Thunder Client</t>
+  </si>
+  <si>
+    <t>Postman</t>
+  </si>
+  <si>
+    <t>Live Server</t>
+  </si>
+  <si>
+    <t>Extensión de VS Code para pruebas de API ligera y rápida.</t>
+  </si>
+  <si>
+    <t>Realizar peticiones HTTP (GET, POST) directamente desde el editor de código.</t>
+  </si>
+  <si>
+    <t>Plataforma completa para el desarrollo y pruebas de APIs.</t>
+  </si>
+  <si>
+    <t>Pruebas exhaustivas, automatización de tests y documentación de servicios web.</t>
+  </si>
+  <si>
+    <t>Extensión que lanza un servidor de desarrollo local con recarga automática.</t>
+  </si>
+  <si>
+    <t>Visualización en tiempo real de cambios en archivos HTML, CSS y JavaScript.</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>Github</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,17 +455,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -433,11 +491,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,6 +515,1189 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>124240</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>48258</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>597018</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>519495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1029" name="Picture 5" descr="Archivo:HTML5 logo and wordmark.svg - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="886240" y="636323"/>
+          <a:ext cx="472778" cy="471237"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>27332</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>541805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1030" name="Picture 6" descr="Archivo:CSS3 logo and wordmark.svg - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="942975" y="1186897"/>
+          <a:ext cx="361950" cy="514473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>140807</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>50335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>599992</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>513109</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1031" name="Picture 7" descr="Archivo:Typescript logo 2020.svg - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="902807" y="1781400"/>
+          <a:ext cx="459185" cy="462774"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>542925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1032" name="Picture 8" descr="Archivo:Angular gradient logo.png - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6827768" y="607115"/>
+          <a:ext cx="523875" cy="523875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>545307</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="11 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6829425" y="1190626"/>
+          <a:ext cx="542925" cy="526256"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>132528</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>49694</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>613773</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>533485</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1035" name="Picture 11" descr="primeng-logo – PrimeFaces"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12854615" y="637759"/>
+          <a:ext cx="481245" cy="483791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>71585</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>100574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>697514</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>486157</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1036" name="Picture 12" descr="Archivo:Tailwind CSS Logo.svg - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12793672" y="1260139"/>
+          <a:ext cx="625929" cy="385583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>132528</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>49698</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>592089</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>513525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="15 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12854615" y="1780763"/>
+          <a:ext cx="459561" cy="463827"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>74547</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>16566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>596351</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>537091</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="18 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12796634" y="2890631"/>
+          <a:ext cx="521804" cy="520525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>99395</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>49782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>571504</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>521450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1039" name="Picture 15" descr="RxJS"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12821482" y="3495347"/>
+          <a:ext cx="472109" cy="471668"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>115952</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>556207</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>505240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1040" name="Picture 16" descr="Argon2 Hash Generator, Validator &amp; Verifier"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12838039" y="4083326"/>
+          <a:ext cx="440255" cy="438979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>33132</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>33129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>670893</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>10619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1041" name="Picture 17" descr="Nodemailer – Send e-mails with Node.JS"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12755219" y="4621694"/>
+          <a:ext cx="637761" cy="548990"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>57980</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>637763</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>539550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1042" name="Picture 18" descr="Archivo:Pg logo.png - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12780067" y="5176630"/>
+          <a:ext cx="579783" cy="522985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>134503</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>521808</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1043" name="Picture 19" descr="SVG (vector) Logo · Issue #7482 · typeorm/typeorm"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12722087" y="5797829"/>
+          <a:ext cx="896503" cy="455544"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>459265</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>33129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>960686</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>538370</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1044" name="Picture 20" descr="VSC-logo – No Blinky Blinky"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19936248" y="617767"/>
+          <a:ext cx="501421" cy="505241"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>467548</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>41416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>939656</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>517804</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1045" name="Picture 21" descr="Archivo:Dia.svg - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19943372" y="1206828"/>
+          <a:ext cx="472108" cy="476388"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>550367</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>41415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>856823</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>503213</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="27 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20027350" y="1769053"/>
+          <a:ext cx="306456" cy="461798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>351586</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>41416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1078950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>527497</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="29 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19828569" y="2340554"/>
+          <a:ext cx="727364" cy="486081"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>460978</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>74260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>898867</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>479535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1048" name="Picture 24" descr="Archivo:Microsoft Office Word (2019–2025).svg - Wikipedia, la enciclopedia  libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19937961" y="3516398"/>
+          <a:ext cx="437889" cy="405275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>467547</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66265</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>909564</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>488677</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1049" name="Picture 25" descr="Archivo:Microsoft Office Excel (2019–2025).svg - Wikipedia, la enciclopedia  libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19944530" y="2936903"/>
+          <a:ext cx="442017" cy="422412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>453261</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>52554</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>901531</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>512380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1050" name="Picture 26" descr="Archivo:Google Drive logo.png - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19930244" y="4066192"/>
+          <a:ext cx="448270" cy="459826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>39413</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>131380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>85397</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>440803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="34 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19516396" y="4716518"/>
+          <a:ext cx="1445173" cy="309423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>446690</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>906518</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>520935</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="36 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19923673" y="5196052"/>
+          <a:ext cx="459828" cy="481521"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>91110</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>41414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>604632</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>554936</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="37 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12813197" y="2343979"/>
+          <a:ext cx="513522" cy="513522"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>69272</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25111</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>612197</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>551367</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="38 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12794672" y="6330661"/>
+          <a:ext cx="542925" cy="526256"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>414622</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>918886</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>537766</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1392" name="Picture 368" descr="Thunder Client - Visual Studio Marketplace"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19890446" y="5771030"/>
+          <a:ext cx="504264" cy="504148"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>470604</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>44425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>935936</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>509414</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="42 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19934734" y="6347490"/>
+          <a:ext cx="465332" cy="464989"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>347383</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>537884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1019735</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="44 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19823207" y="6846796"/>
+          <a:ext cx="672352" cy="672352"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>462642</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>952499</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>530678</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1081" name="Picture 57" descr="Jira - Iconos gratis de logo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="20301856" y="7497535"/>
+          <a:ext cx="489857" cy="489857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>435428</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>557893</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1083" name="Picture 59" descr="Logotipo de github - Iconos gratis de redes sociales"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="20274642" y="8069035"/>
+          <a:ext cx="517072" cy="517072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,7 +1743,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,10 +1775,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -566,7 +1809,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -742,359 +1984,420 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:U14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:U17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" customWidth="1"/>
     <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" customWidth="1"/>
     <col min="15" max="15" width="28.42578125" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21" customWidth="1"/>
+    <col min="19" max="19" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="27" customWidth="1"/>
     <col min="21" max="21" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+    <row r="1" spans="2:21" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:21">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="G2" s="8" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="10"/>
-      <c r="L2" s="8" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+      <c r="L2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="10"/>
-      <c r="R2" s="8" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="12"/>
+      <c r="R2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="10"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="B4" s="15"/>
+      <c r="C4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="6"/>
+      <c r="M4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="1"/>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="6"/>
+      <c r="S4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="T4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="U4" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="B5" s="15"/>
+      <c r="C5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="4" t="s">
+      <c r="L5" s="6"/>
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="6"/>
+      <c r="S5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="B6" s="15"/>
+      <c r="C6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="I6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="J6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="4" t="s">
+      <c r="L6" s="4"/>
+      <c r="M6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="4"/>
+      <c r="S6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="T6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="U6" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="R6" s="1"/>
-      <c r="S6" s="2" t="s">
+    <row r="7" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L7" s="6"/>
+      <c r="M7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R7" s="6"/>
+      <c r="S7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="T7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="U6" s="12" t="s">
+      <c r="U7" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L7" s="3"/>
-      <c r="M7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="R7" s="3"/>
-      <c r="S7" s="4" t="s">
+    <row r="8" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L8" s="4"/>
+      <c r="M8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="4"/>
+      <c r="S8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="U8" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="2" t="s">
+    <row r="9" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L9" s="6"/>
+      <c r="M9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" s="6"/>
+      <c r="S9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="11" t="s">
+      <c r="T9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U8" s="12" t="s">
+      <c r="U9" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L9" s="3"/>
-      <c r="M9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="4" t="s">
+    <row r="10" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L10" s="4"/>
+      <c r="M10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="R10" s="4"/>
+      <c r="S10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="T10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="U9" s="12" t="s">
+      <c r="U10" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L10" s="1"/>
-      <c r="M10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="R10" s="1"/>
-      <c r="S10" s="2" t="s">
+    <row r="11" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L11" s="6"/>
+      <c r="M11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" s="6"/>
+      <c r="S11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="T10" s="11" t="s">
+      <c r="T11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U11" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L11" s="3"/>
-      <c r="M11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="R11" s="3"/>
-      <c r="S11" s="4" t="s">
+    <row r="12" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L12" s="4"/>
+      <c r="M12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R12" s="6"/>
+      <c r="S12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="T12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U11" s="12" t="s">
+      <c r="U12" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L12" s="1"/>
-      <c r="M12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>61</v>
+    <row r="13" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="L13" s="6"/>
+      <c r="M13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L13" s="3"/>
-      <c r="M13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>63</v>
+    <row r="14" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="R14" s="6"/>
+      <c r="S14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L14" s="1"/>
-      <c r="M14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>65</v>
-      </c>
+    <row r="15" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="R15" s="6"/>
+      <c r="S15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" ht="45" customHeight="1" thickBot="1">
+      <c r="R16" s="6"/>
+      <c r="S16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="18:21" ht="45" customHeight="1" thickBot="1">
+      <c r="R17" s="6"/>
+      <c r="S17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T17" s="2"/>
+      <c r="U17" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1105,13 +2408,14 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -1119,9 +2423,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>

--- a/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
+++ b/Proyecto Intermodular/Tablas/Tecnologías y herramientas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="300" windowWidth="14880" windowHeight="7815"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t>Icono</t>
   </si>
@@ -39,9 +39,6 @@
     <t>TS</t>
   </si>
   <si>
-    <t>Lenguages</t>
-  </si>
-  <si>
     <t>Frameworks</t>
   </si>
   <si>
@@ -84,12 +81,6 @@
     <t>typeorm</t>
   </si>
   <si>
-    <t>websockets</t>
-  </si>
-  <si>
-    <t>Herramientas</t>
-  </si>
-  <si>
     <t>Visual Studio Code</t>
   </si>
   <si>
@@ -117,9 +108,6 @@
     <t>Lenguaje de marcado para estructurar el contenido de páginas web.</t>
   </si>
   <si>
-    <t>Crear la estructura base de interfaces web y aplicaciones.</t>
-  </si>
-  <si>
     <t>Lenguaje de estilos para definir el diseño y apariencia visual.</t>
   </si>
   <si>
@@ -129,21 +117,12 @@
     <t>Superset de JavaScript que añade tipado estático y mejoras.</t>
   </si>
   <si>
-    <t>Desarrollo más seguro y mantenible en aplicaciones grandes.</t>
-  </si>
-  <si>
     <t>Framework frontend basado en TypeScript para SPA.</t>
   </si>
   <si>
-    <t>Crear aplicaciones web escalables y estructuradas.</t>
-  </si>
-  <si>
     <t>Framework backend para Node.js basado en arquitectura modular.</t>
   </si>
   <si>
-    <t>Construcción de APIs robustas y mantenibles.</t>
-  </si>
-  <si>
     <t>Biblioteca de componentes UI para Angular.</t>
   </si>
   <si>
@@ -153,9 +132,6 @@
     <t>Framework CSS basado en clases utilitarias.</t>
   </si>
   <si>
-    <t>Maquetación rápida y diseño flexible sin CSS tradicional.</t>
-  </si>
-  <si>
     <t>Cliente para comunicación en tiempo real vía WebSockets.</t>
   </si>
   <si>
@@ -201,27 +177,12 @@
     <t>Cliente PostgreSQL para Node.js.</t>
   </si>
   <si>
-    <t>Conexión y consultas a bases de datos PostgreSQL.</t>
-  </si>
-  <si>
     <t>ORM para TypeScript y JavaScript.</t>
   </si>
   <si>
-    <t>Mapeo y gestión de bases de datos relacionales.</t>
-  </si>
-  <si>
-    <t>Protocolo de comunicación bidireccional en tiempo real.</t>
-  </si>
-  <si>
-    <t>Comunicación instantánea entre cliente y servidor.</t>
-  </si>
-  <si>
     <t>Editor de código ligero y extensible.</t>
   </si>
   <si>
-    <t>Desarrollo y depuración de aplicaciones.</t>
-  </si>
-  <si>
     <t>Herramienta para diagramas y esquemas.</t>
   </si>
   <si>
@@ -264,9 +225,6 @@
     <t>Herramienta de administración y desarrollo para PostgreSQL.</t>
   </si>
   <si>
-    <t>Gestión de bases de datos, ejecución de consultas SQL y diseño de esquemas.</t>
-  </si>
-  <si>
     <t>Thunder Client</t>
   </si>
   <si>
@@ -279,15 +237,9 @@
     <t>Extensión de VS Code para pruebas de API ligera y rápida.</t>
   </si>
   <si>
-    <t>Realizar peticiones HTTP (GET, POST) directamente desde el editor de código.</t>
-  </si>
-  <si>
     <t>Plataforma completa para el desarrollo y pruebas de APIs.</t>
   </si>
   <si>
-    <t>Pruebas exhaustivas, automatización de tests y documentación de servicios web.</t>
-  </si>
-  <si>
     <t>Extensión que lanza un servidor de desarrollo local con recarga automática.</t>
   </si>
   <si>
@@ -298,17 +250,107 @@
   </si>
   <si>
     <t>Github</t>
+  </si>
+  <si>
+    <t>Herramientas y Extensiones</t>
+  </si>
+  <si>
+    <t>AWS EC2</t>
+  </si>
+  <si>
+    <t>AWS RDS</t>
+  </si>
+  <si>
+    <t>AWS S3</t>
+  </si>
+  <si>
+    <t>Lenguajes</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Plataforma de gestión de proyectos basada en metodologías ágiles (Scrum/Kanban).</t>
+  </si>
+  <si>
+    <t>Plataforma de alojamiento de código basada en Git con herramientas de colaboración.</t>
+  </si>
+  <si>
+    <t>Servicio de servidores virtuales elásticos en la nube (Elastic Compute Cloud).</t>
+  </si>
+  <si>
+    <t>Servicio de bases de datos relacionales administradas (Relational Database Service).</t>
+  </si>
+  <si>
+    <t>Servicio de almacenamiento de objetos escalable (Simple Storage Service).</t>
+  </si>
+  <si>
+    <t>Crear la estructura de elemtnos de la página web</t>
+  </si>
+  <si>
+    <t>Desarrollo seguro y mantenible dando funcionalidad a la aplicación</t>
+  </si>
+  <si>
+    <t>Desarrollar el front de la aplicación web</t>
+  </si>
+  <si>
+    <t>Maquetar con un diseño flexible sin CSS tradicional.</t>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+  </si>
+  <si>
+    <t>Lenguaje de consulta estructurado para la gestión de bases de datos relacionales.</t>
+  </si>
+  <si>
+    <t>Definir esquemas, manipular datos (CRUD) y realizar consultas complejas en la base de datos.</t>
+  </si>
+  <si>
+    <t>Mapeo y gestión dela base de datos</t>
+  </si>
+  <si>
+    <t>Conexión y consultas a la base de datos PostgreSQL</t>
+  </si>
+  <si>
+    <t>Alojamiento y despliegue del front y la API.</t>
+  </si>
+  <si>
+    <t>Hosting y escalado de PostgreSQL, con alta disponibilidad.</t>
+  </si>
+  <si>
+    <t>Almacenamiento de archivos estáticos, imágenes y recursos multimedia de la aplicación.</t>
+  </si>
+  <si>
+    <t>Desarrollo y depuración del código de la aplicación web.</t>
+  </si>
+  <si>
+    <t>Gestión de la base de datos</t>
+  </si>
+  <si>
+    <t>Prueba de peticiones HTTP (GET, POST) directamente desde el editor de código.</t>
+  </si>
+  <si>
+    <t>Pruebas exhaustivas de servicios web.</t>
+  </si>
+  <si>
+    <t>Seguimiento de tareas, planificación de sprints y control del ciclo de vida del desarrollo.</t>
+  </si>
+  <si>
+    <t>Control de versiones, revisión de código y automatización de despliegues (CI/CD).</t>
+  </si>
+  <si>
+    <t>Construir la API que hace de nexto entre el front y la base de datos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,48 +499,50 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1076,13 +1120,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>459265</xdr:colOff>
+      <xdr:colOff>227945</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>33129</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>960686</xdr:colOff>
+      <xdr:colOff>729366</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>538370</xdr:rowOff>
     </xdr:to>
@@ -1102,7 +1146,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19936248" y="617767"/>
+          <a:off x="20067159" y="631843"/>
           <a:ext cx="501421" cy="505241"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1116,13 +1160,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>467548</xdr:colOff>
+      <xdr:colOff>236228</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>41416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>939656</xdr:colOff>
+      <xdr:colOff>708336</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>517804</xdr:rowOff>
     </xdr:to>
@@ -1142,7 +1186,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19943372" y="1206828"/>
+          <a:off x="20075442" y="1783130"/>
           <a:ext cx="472108" cy="476388"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1156,33 +1200,71 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>550367</xdr:colOff>
+      <xdr:colOff>319047</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>41415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>625503</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>503213</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="27 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20158261" y="4640629"/>
+          <a:ext cx="306456" cy="461798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>120266</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>41415</xdr:rowOff>
+      <xdr:rowOff>41416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>856823</xdr:colOff>
+      <xdr:colOff>847630</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>503213</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="27 Imagen"/>
+      <xdr:rowOff>527497</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="29 Imagen"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20027350" y="1769053"/>
-          <a:ext cx="306456" cy="461798"/>
+          <a:off x="19959480" y="2354630"/>
+          <a:ext cx="727364" cy="486081"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1194,52 +1276,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>351586</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>41416</xdr:rowOff>
+      <xdr:colOff>229658</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>74260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>1078950</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>527497</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="29 Imagen"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19828569" y="2340554"/>
-          <a:ext cx="727364" cy="486081"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>460978</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>74260</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>898867</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:colOff>667547</xdr:colOff>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>479535</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1258,7 +1302,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19937961" y="3516398"/>
+          <a:off x="20068872" y="3530474"/>
           <a:ext cx="437889" cy="405275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1272,14 +1316,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>467547</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:colOff>236227</xdr:colOff>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>66265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>909564</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:colOff>678244</xdr:colOff>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>488677</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1298,7 +1342,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19944530" y="2936903"/>
+          <a:off x="20075441" y="2950979"/>
           <a:ext cx="442017" cy="422412"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1312,14 +1356,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>453261</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:colOff>221941</xdr:colOff>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>52554</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>901531</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:colOff>670211</xdr:colOff>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>512380</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1338,7 +1382,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19930244" y="4066192"/>
+          <a:off x="20061155" y="4080268"/>
           <a:ext cx="448270" cy="459826"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1351,52 +1395,52 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>66627</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>1514147</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>440803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="34 Imagen"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26614163" y="2444594"/>
+          <a:ext cx="1447520" cy="309423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>39413</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>131380</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>85397</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>440803</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="34 Imagen"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19516396" y="4716518"/>
-          <a:ext cx="1445173" cy="309423"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>446690</xdr:colOff>
+      <xdr:colOff>215370</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>39414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>906518</xdr:colOff>
+      <xdr:colOff>675198</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>520935</xdr:rowOff>
     </xdr:to>
@@ -1415,7 +1459,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19923673" y="5196052"/>
+          <a:off x="20054584" y="1209628"/>
           <a:ext cx="459828" cy="481521"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1465,53 +1509,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>69272</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>25111</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>612197</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>551367</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="38 Imagen"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12794672" y="6330661"/>
-          <a:ext cx="542925" cy="526256"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>414622</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:colOff>183302</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>33618</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>918886</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:colOff>687566</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>537766</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1530,7 +1536,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="19890446" y="5771030"/>
+          <a:off x="20022516" y="5204332"/>
           <a:ext cx="504264" cy="504148"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1544,14 +1550,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>470604</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>239284</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>44425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>935936</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>704616</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>509414</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1569,7 +1575,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19934734" y="6347490"/>
+          <a:off x="20078498" y="5786639"/>
           <a:ext cx="465332" cy="464989"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1582,14 +1588,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>347383</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>116063</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>537884</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>1019735</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:colOff>788415</xdr:colOff>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>67236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1607,7 +1613,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19823207" y="6846796"/>
+          <a:off x="19955277" y="6280098"/>
           <a:ext cx="672352" cy="672352"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1620,54 +1626,54 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>462642</xdr:colOff>
+      <xdr:colOff>231322</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>721179</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>530678</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1081" name="Picture 57" descr="Jira - Iconos gratis de logo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="20070536" y="6926035"/>
+          <a:ext cx="489857" cy="489857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>40821</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>952499</xdr:colOff>
+      <xdr:colOff>721180</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>530678</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1081" name="Picture 57" descr="Jira - Iconos gratis de logo"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="20301856" y="7497535"/>
-          <a:ext cx="489857" cy="489857"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>435428</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>16</xdr:row>
       <xdr:rowOff>557893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1686,8 +1692,179 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="20274642" y="8069035"/>
+          <a:off x="20043322" y="7497535"/>
           <a:ext cx="517072" cy="517072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>547426</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>43961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>1037283</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>533818</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27136830" y="630115"/>
+          <a:ext cx="489857" cy="489857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>542193</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>43963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>1040424</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>542535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Imagen 35" descr="AWS Observability integrations | Sumo Logic Docs"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="27131597" y="1201617"/>
+          <a:ext cx="498231" cy="498572"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>549520</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>534498</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27138924" y="1765790"/>
+          <a:ext cx="498230" cy="497862"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>87923</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>29307</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>667706</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>552292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 18" descr="Archivo:Pg logo.png - Wikipedia, la enciclopedia libre"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="849923" y="2329961"/>
+          <a:ext cx="579783" cy="522985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1743,7 +1920,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1775,9 +1952,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1809,6 +1987,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1984,427 +2163,493 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:U17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:Z17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
-    <col min="10" max="10" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27" customWidth="1"/>
-    <col min="15" max="15" width="28.42578125" customWidth="1"/>
-    <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27" customWidth="1"/>
-    <col min="21" max="21" width="28.42578125" customWidth="1"/>
+    <col min="1" max="3" width="11.42578125" style="1"/>
+    <col min="4" max="4" width="27" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="11.42578125" style="1"/>
+    <col min="9" max="9" width="27" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27" style="1" customWidth="1"/>
+    <col min="15" max="15" width="28.42578125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="11.42578125" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="19.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27" style="1" customWidth="1"/>
+    <col min="21" max="21" width="28.42578125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" style="1"/>
+    <col min="23" max="23" width="23.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="19.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27" style="1" customWidth="1"/>
+    <col min="26" max="26" width="28.42578125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:21">
-      <c r="B2" s="10" t="s">
+    <row r="1" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="G2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12"/>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="15"/>
+      <c r="L2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="15"/>
+      <c r="R2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="15"/>
+      <c r="W2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="15"/>
+    </row>
+    <row r="3" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5"/>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="12"/>
-      <c r="L2" s="10" t="s">
+      <c r="I4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12"/>
-      <c r="R2" s="10" t="s">
+      <c r="N4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="9"/>
+      <c r="S4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="W4" s="9"/>
+      <c r="X4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="9"/>
+      <c r="S5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="W5" s="9"/>
+      <c r="X5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+      <c r="C6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" s="5"/>
+      <c r="X6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5"/>
+      <c r="C7" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="W7" s="5"/>
+      <c r="X7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="5"/>
+      <c r="M8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="R8" s="9"/>
+      <c r="S8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="9"/>
+      <c r="M9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R9" s="5"/>
+      <c r="S9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="5"/>
+      <c r="M10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="9"/>
+      <c r="S10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="9"/>
+      <c r="M11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="R11" s="9"/>
+      <c r="S11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="12"/>
+      <c r="T11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="3" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>3</v>
+    <row r="12" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="5"/>
+      <c r="M12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="R12" s="5"/>
+      <c r="S12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="B4" s="15"/>
-      <c r="C4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>67</v>
+    <row r="13" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="9"/>
+      <c r="S13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="B5" s="15"/>
-      <c r="C5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>82</v>
+    <row r="14" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="9"/>
+      <c r="S14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="B6" s="15"/>
-      <c r="C6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>69</v>
+    <row r="15" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="9"/>
+      <c r="S15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L7" s="6"/>
-      <c r="M7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="R7" s="6"/>
-      <c r="S7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>71</v>
+    <row r="16" spans="2:26" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="9"/>
+      <c r="S16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="T16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L8" s="4"/>
-      <c r="M8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L9" s="6"/>
-      <c r="M9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L10" s="4"/>
-      <c r="M10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L11" s="6"/>
-      <c r="M11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L12" s="4"/>
-      <c r="M12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R12" s="6"/>
-      <c r="S12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="L13" s="6"/>
-      <c r="M13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="R14" s="6"/>
-      <c r="S14" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="R15" s="6"/>
-      <c r="S15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" ht="45" customHeight="1" thickBot="1">
-      <c r="R16" s="6"/>
-      <c r="S16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="T16" s="2"/>
-      <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="18:21" ht="45" customHeight="1" thickBot="1">
-      <c r="R17" s="6"/>
-      <c r="S17" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="T17" s="2"/>
-      <c r="U17" s="3"/>
-    </row>
+    <row r="17" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="R2:U2"/>
+    <mergeCell ref="W2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -2413,9 +2658,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -2423,9 +2668,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
